--- a/SISAB/dados/consolidado_final_com_urgencia.xlsx
+++ b/SISAB/dados/consolidado_final_com_urgencia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y163"/>
+  <dimension ref="A1:AA163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +554,16 @@
           <t>populacao_ibge</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dependentes_do_sus</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>percentual_dependentes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -633,6 +643,12 @@
       <c r="Y2" t="n">
         <v>75000</v>
       </c>
+      <c r="Z2" t="n">
+        <v>68509</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.9134533333333333</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -712,6 +728,12 @@
       <c r="Y3" t="n">
         <v>72000</v>
       </c>
+      <c r="Z3" t="n">
+        <v>65313</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.907125</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -791,6 +813,12 @@
       <c r="Y4" t="n">
         <v>83000</v>
       </c>
+      <c r="Z4" t="n">
+        <v>76244</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.9186024096385542</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -870,6 +898,12 @@
       <c r="Y5" t="n">
         <v>83000</v>
       </c>
+      <c r="Z5" t="n">
+        <v>76234</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.9184819277108434</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -949,6 +983,12 @@
       <c r="Y6" t="n">
         <v>86000</v>
       </c>
+      <c r="Z6" t="n">
+        <v>78932</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.9178139534883721</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1028,6 +1068,12 @@
       <c r="Y7" t="n">
         <v>92694</v>
       </c>
+      <c r="Z7" t="n">
+        <v>85318</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.9204263490625068</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1107,6 +1153,12 @@
       <c r="Y8" t="n">
         <v>420000</v>
       </c>
+      <c r="Z8" t="n">
+        <v>371191</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.8837880952380952</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1186,6 +1238,12 @@
       <c r="Y9" t="n">
         <v>364000</v>
       </c>
+      <c r="Z9" t="n">
+        <v>312886</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.8595769230769231</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1265,6 +1323,12 @@
       <c r="Y10" t="n">
         <v>388000</v>
       </c>
+      <c r="Z10" t="n">
+        <v>334816</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.8629278350515464</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1344,6 +1408,12 @@
       <c r="Y11" t="n">
         <v>400000</v>
       </c>
+      <c r="Z11" t="n">
+        <v>345082</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.8627050000000001</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1423,6 +1493,12 @@
       <c r="Y12" t="n">
         <v>421000</v>
       </c>
+      <c r="Z12" t="n">
+        <v>364792</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.8664893111638955</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1502,6 +1578,12 @@
       <c r="Y13" t="n">
         <v>482240</v>
       </c>
+      <c r="Z13" t="n">
+        <v>424896</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.8810882548108826</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1581,6 +1663,12 @@
       <c r="Y14" t="n">
         <v>323000</v>
       </c>
+      <c r="Z14" t="n">
+        <v>285403</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.8836006191950464</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1660,6 +1748,12 @@
       <c r="Y15" t="n">
         <v>372000</v>
       </c>
+      <c r="Z15" t="n">
+        <v>333589</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.896744623655914</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1739,6 +1833,12 @@
       <c r="Y16" t="n">
         <v>367000</v>
       </c>
+      <c r="Z16" t="n">
+        <v>326626</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.8899891008174386</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1818,6 +1918,12 @@
       <c r="Y17" t="n">
         <v>368000</v>
       </c>
+      <c r="Z17" t="n">
+        <v>325581</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.8847309782608695</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1897,6 +2003,12 @@
       <c r="Y18" t="n">
         <v>445000</v>
       </c>
+      <c r="Z18" t="n">
+        <v>400141</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.8991932584269663</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1976,6 +2088,12 @@
       <c r="Y19" t="n">
         <v>428930</v>
       </c>
+      <c r="Z19" t="n">
+        <v>369842</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.8622432564754156</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2055,6 +2173,12 @@
       <c r="Y20" t="n">
         <v>59000</v>
       </c>
+      <c r="Z20" t="n">
+        <v>51166</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.8672203389830508</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2134,6 +2258,12 @@
       <c r="Y21" t="n">
         <v>67000</v>
       </c>
+      <c r="Z21" t="n">
+        <v>60227</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.898910447761194</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2213,6 +2343,12 @@
       <c r="Y22" t="n">
         <v>71000</v>
       </c>
+      <c r="Z22" t="n">
+        <v>63378</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.8926478873239436</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2292,6 +2428,12 @@
       <c r="Y23" t="n">
         <v>80000</v>
       </c>
+      <c r="Z23" t="n">
+        <v>72041</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.9005125</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2371,6 +2513,12 @@
       <c r="Y24" t="n">
         <v>74000</v>
       </c>
+      <c r="Z24" t="n">
+        <v>66088</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.8930810810810811</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2450,6 +2598,12 @@
       <c r="Y25" t="n">
         <v>82788</v>
       </c>
+      <c r="Z25" t="n">
+        <v>74302</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.8974972218195874</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2529,6 +2683,12 @@
       <c r="Y26" t="n">
         <v>1984000</v>
       </c>
+      <c r="Z26" t="n">
+        <v>1796776</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.905633064516129</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2608,6 +2768,12 @@
       <c r="Y27" t="n">
         <v>2153000</v>
       </c>
+      <c r="Z27" t="n">
+        <v>1958299</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.9095675801207618</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2687,6 +2853,12 @@
       <c r="Y28" t="n">
         <v>2177000</v>
       </c>
+      <c r="Z28" t="n">
+        <v>1977164</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.9082057877813505</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2766,6 +2938,12 @@
       <c r="Y29" t="n">
         <v>2213000</v>
       </c>
+      <c r="Z29" t="n">
+        <v>2002653</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.9049493899683687</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2845,6 +3023,12 @@
       <c r="Y30" t="n">
         <v>2356000</v>
       </c>
+      <c r="Z30" t="n">
+        <v>2137329</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.9071854838709678</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2924,6 +3108,12 @@
       <c r="Y31" t="n">
         <v>2496228</v>
       </c>
+      <c r="Z31" t="n">
+        <v>2266645</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.9080280326957313</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3003,6 +3193,12 @@
       <c r="Y32" t="n">
         <v>1225000</v>
       </c>
+      <c r="Z32" t="n">
+        <v>1087096</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.887425306122449</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3082,6 +3278,12 @@
       <c r="Y33" t="n">
         <v>1218000</v>
       </c>
+      <c r="Z33" t="n">
+        <v>1075827</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.8832733990147783</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3161,6 +3363,12 @@
       <c r="Y34" t="n">
         <v>1372000</v>
       </c>
+      <c r="Z34" t="n">
+        <v>1224933</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.8928083090379009</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3240,6 +3448,12 @@
       <c r="Y35" t="n">
         <v>1352000</v>
       </c>
+      <c r="Z35" t="n">
+        <v>1198626</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.8865576923076923</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3319,6 +3533,12 @@
       <c r="Y36" t="n">
         <v>1523000</v>
       </c>
+      <c r="Z36" t="n">
+        <v>1361138</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.8937216021011162</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3398,6 +3618,12 @@
       <c r="Y37" t="n">
         <v>1501253</v>
       </c>
+      <c r="Z37" t="n">
+        <v>1331142</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.8866873205249215</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3477,6 +3703,12 @@
       <c r="Y38" t="n">
         <v>349000</v>
       </c>
+      <c r="Z38" t="n">
+        <v>225629</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.6465014326647565</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3556,6 +3788,12 @@
       <c r="Y39" t="n">
         <v>317000</v>
       </c>
+      <c r="Z39" t="n">
+        <v>183768</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.5797097791798107</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3635,6 +3873,12 @@
       <c r="Y40" t="n">
         <v>330000</v>
       </c>
+      <c r="Z40" t="n">
+        <v>200590</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.6078484848484849</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3714,6 +3958,12 @@
       <c r="Y41" t="n">
         <v>383000</v>
       </c>
+      <c r="Z41" t="n">
+        <v>246408</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.6433629242819844</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3793,6 +4043,12 @@
       <c r="Y42" t="n">
         <v>400000</v>
       </c>
+      <c r="Z42" t="n">
+        <v>256551</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.6413775</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3872,6 +4128,12 @@
       <c r="Y43" t="n">
         <v>473870</v>
       </c>
+      <c r="Z43" t="n">
+        <v>319068</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.673323907400764</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3951,6 +4213,12 @@
       <c r="Y44" t="n">
         <v>539000</v>
       </c>
+      <c r="Z44" t="n">
+        <v>398899</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.7400723562152134</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4030,6 +4298,12 @@
       <c r="Y45" t="n">
         <v>562000</v>
       </c>
+      <c r="Z45" t="n">
+        <v>410461</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.7303576512455516</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4109,6 +4383,12 @@
       <c r="Y46" t="n">
         <v>607000</v>
       </c>
+      <c r="Z46" t="n">
+        <v>446641</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.7358171334431631</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4188,6 +4468,12 @@
       <c r="Y47" t="n">
         <v>642000</v>
       </c>
+      <c r="Z47" t="n">
+        <v>474883</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.7396931464174454</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4267,6 +4553,12 @@
       <c r="Y48" t="n">
         <v>671000</v>
       </c>
+      <c r="Z48" t="n">
+        <v>497076</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.7407988077496275</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4346,6 +4638,12 @@
       <c r="Y49" t="n">
         <v>783156</v>
       </c>
+      <c r="Z49" t="n">
+        <v>597622</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.7630944537231408</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4425,6 +4723,12 @@
       <c r="Y50" t="n">
         <v>863000</v>
       </c>
+      <c r="Z50" t="n">
+        <v>755526</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.8754646581691773</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4504,6 +4808,12 @@
       <c r="Y51" t="n">
         <v>977000</v>
       </c>
+      <c r="Z51" t="n">
+        <v>740210</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.7576356192425793</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4583,6 +4893,12 @@
       <c r="Y52" t="n">
         <v>913000</v>
       </c>
+      <c r="Z52" t="n">
+        <v>663405</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0.7266210295728368</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4662,6 +4978,12 @@
       <c r="Y53" t="n">
         <v>1005000</v>
       </c>
+      <c r="Z53" t="n">
+        <v>738258</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.7345850746268656</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4741,6 +5063,12 @@
       <c r="Y54" t="n">
         <v>984000</v>
       </c>
+      <c r="Z54" t="n">
+        <v>699847</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.7112266260162602</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4820,6 +5148,12 @@
       <c r="Y55" t="n">
         <v>1137176</v>
       </c>
+      <c r="Z55" t="n">
+        <v>835796</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0.7349750610283721</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4899,6 +5233,12 @@
       <c r="Y56" t="n">
         <v>771000</v>
       </c>
+      <c r="Z56" t="n">
+        <v>722073</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0.9365408560311284</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4978,6 +5318,12 @@
       <c r="Y57" t="n">
         <v>751000</v>
       </c>
+      <c r="Z57" t="n">
+        <v>707663</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0.942294274300932</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5057,6 +5403,12 @@
       <c r="Y58" t="n">
         <v>829000</v>
       </c>
+      <c r="Z58" t="n">
+        <v>784475</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0.9462907117008444</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5136,6 +5488,12 @@
       <c r="Y59" t="n">
         <v>818000</v>
       </c>
+      <c r="Z59" t="n">
+        <v>771521</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0.943179706601467</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5215,6 +5573,12 @@
       <c r="Y60" t="n">
         <v>903000</v>
       </c>
+      <c r="Z60" t="n">
+        <v>854329</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0.9461007751937984</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5294,6 +5658,12 @@
       <c r="Y61" t="n">
         <v>917723</v>
       </c>
+      <c r="Z61" t="n">
+        <v>867117</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0.9448569993342217</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5373,6 +5743,12 @@
       <c r="Y62" t="n">
         <v>3103000</v>
       </c>
+      <c r="Z62" t="n">
+        <v>2392436</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0.7710074121817596</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5452,6 +5828,12 @@
       <c r="Y63" t="n">
         <v>3220000</v>
       </c>
+      <c r="Z63" t="n">
+        <v>2462668</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0.7648037267080745</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5531,6 +5913,12 @@
       <c r="Y64" t="n">
         <v>3332000</v>
       </c>
+      <c r="Z64" t="n">
+        <v>2543765</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.7634348739495799</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5610,6 +5998,12 @@
       <c r="Y65" t="n">
         <v>3468000</v>
       </c>
+      <c r="Z65" t="n">
+        <v>2649633</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0.7640233564013841</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5689,6 +6083,12 @@
       <c r="Y66" t="n">
         <v>3589000</v>
       </c>
+      <c r="Z66" t="n">
+        <v>2737219</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0.762668988576205</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5768,6 +6168,12 @@
       <c r="Y67" t="n">
         <v>4420482</v>
       </c>
+      <c r="Z67" t="n">
+        <v>3541443</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0.8011440833827623</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5847,6 +6253,12 @@
       <c r="Y68" t="n">
         <v>328000</v>
       </c>
+      <c r="Z68" t="n">
+        <v>250317</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0.7631615853658537</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5926,6 +6338,12 @@
       <c r="Y69" t="n">
         <v>340000</v>
       </c>
+      <c r="Z69" t="n">
+        <v>258636</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.7606941176470589</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6005,6 +6423,12 @@
       <c r="Y70" t="n">
         <v>352000</v>
       </c>
+      <c r="Z70" t="n">
+        <v>267397</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0.7596505681818182</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6084,6 +6508,12 @@
       <c r="Y71" t="n">
         <v>374000</v>
       </c>
+      <c r="Z71" t="n">
+        <v>284651</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0.7610989304812834</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6163,6 +6593,12 @@
       <c r="Y72" t="n">
         <v>384000</v>
       </c>
+      <c r="Z72" t="n">
+        <v>290025</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0.7552734375</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6242,6 +6678,12 @@
       <c r="Y73" t="n">
         <v>482355</v>
       </c>
+      <c r="Z73" t="n">
+        <v>384153</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0.7964113567807942</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6321,6 +6763,12 @@
       <c r="Y74" t="n">
         <v>354000</v>
       </c>
+      <c r="Z74" t="n">
+        <v>304674</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.8606610169491525</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6400,6 +6848,12 @@
       <c r="Y75" t="n">
         <v>407000</v>
       </c>
+      <c r="Z75" t="n">
+        <v>353979</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8697272727272727</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6479,6 +6933,12 @@
       <c r="Y76" t="n">
         <v>415000</v>
       </c>
+      <c r="Z76" t="n">
+        <v>359226</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0.8656048192771084</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6558,6 +7018,12 @@
       <c r="Y77" t="n">
         <v>447000</v>
       </c>
+      <c r="Z77" t="n">
+        <v>387975</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0.8679530201342281</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6637,6 +7103,12 @@
       <c r="Y78" t="n">
         <v>395000</v>
       </c>
+      <c r="Z78" t="n">
+        <v>333892</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0.8452962025316456</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6716,6 +7188,12 @@
       <c r="Y79" t="n">
         <v>523959</v>
       </c>
+      <c r="Z79" t="n">
+        <v>461064</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0.8799619817581147</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6795,6 +7273,12 @@
       <c r="Y80" t="n">
         <v>838000</v>
       </c>
+      <c r="Z80" t="n">
+        <v>757861</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0.9043687350835322</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6874,6 +7358,12 @@
       <c r="Y81" t="n">
         <v>842000</v>
       </c>
+      <c r="Z81" t="n">
+        <v>759491</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0.9020083135391924</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6953,6 +7443,12 @@
       <c r="Y82" t="n">
         <v>871000</v>
       </c>
+      <c r="Z82" t="n">
+        <v>785826</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0.902211251435132</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7032,6 +7528,12 @@
       <c r="Y83" t="n">
         <v>935000</v>
       </c>
+      <c r="Z83" t="n">
+        <v>846364</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0.9052021390374332</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7111,6 +7613,12 @@
       <c r="Y84" t="n">
         <v>947000</v>
       </c>
+      <c r="Z84" t="n">
+        <v>854641</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0.9024720168954593</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7190,6 +7698,12 @@
       <c r="Y85" t="n">
         <v>1012604</v>
       </c>
+      <c r="Z85" t="n">
+        <v>914671</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0.9032859834644145</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7269,6 +7783,12 @@
       <c r="Y86" t="n">
         <v>527000</v>
       </c>
+      <c r="Z86" t="n">
+        <v>461975</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>0.8766129032258064</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7348,6 +7868,12 @@
       <c r="Y87" t="n">
         <v>549000</v>
       </c>
+      <c r="Z87" t="n">
+        <v>482605</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0.8790619307832422</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7427,6 +7953,12 @@
       <c r="Y88" t="n">
         <v>553000</v>
       </c>
+      <c r="Z88" t="n">
+        <v>485120</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0.877251356238698</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7506,6 +8038,12 @@
       <c r="Y89" t="n">
         <v>598000</v>
       </c>
+      <c r="Z89" t="n">
+        <v>527810</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>0.8826254180602007</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7585,6 +8123,12 @@
       <c r="Y90" t="n">
         <v>614000</v>
       </c>
+      <c r="Z90" t="n">
+        <v>540697</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>0.8806140065146579</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7664,6 +8208,12 @@
       <c r="Y91" t="n">
         <v>699915</v>
       </c>
+      <c r="Z91" t="n">
+        <v>623304</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0.8905424230085082</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7743,6 +8293,12 @@
       <c r="Y92" t="n">
         <v>1324000</v>
       </c>
+      <c r="Z92" t="n">
+        <v>1155170</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0.8724848942598187</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7822,6 +8378,12 @@
       <c r="Y93" t="n">
         <v>1171000</v>
       </c>
+      <c r="Z93" t="n">
+        <v>993069</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>0.8480520922288642</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7901,6 +8463,12 @@
       <c r="Y94" t="n">
         <v>1371000</v>
       </c>
+      <c r="Z94" t="n">
+        <v>1187631</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0.8662516411378556</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7980,6 +8548,12 @@
       <c r="Y95" t="n">
         <v>1372000</v>
       </c>
+      <c r="Z95" t="n">
+        <v>1180453</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>0.8603884839650145</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8059,6 +8633,12 @@
       <c r="Y96" t="n">
         <v>1422000</v>
       </c>
+      <c r="Z96" t="n">
+        <v>1224397</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0.8610386779184247</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8138,6 +8718,12 @@
       <c r="Y97" t="n">
         <v>1585203</v>
       </c>
+      <c r="Z97" t="n">
+        <v>1382083</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>0.8718649914238114</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8217,6 +8803,12 @@
       <c r="Y98" t="n">
         <v>468000</v>
       </c>
+      <c r="Z98" t="n">
+        <v>437301</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>0.9344038461538462</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8296,6 +8888,12 @@
       <c r="Y99" t="n">
         <v>487000</v>
       </c>
+      <c r="Z99" t="n">
+        <v>455485</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>0.9352874743326489</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8375,6 +8973,12 @@
       <c r="Y100" t="n">
         <v>467000</v>
       </c>
+      <c r="Z100" t="n">
+        <v>433369</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>0.9279850107066381</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8454,6 +9058,12 @@
       <c r="Y101" t="n">
         <v>499000</v>
       </c>
+      <c r="Z101" t="n">
+        <v>463133</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>0.928122244488978</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8533,6 +9143,12 @@
       <c r="Y102" t="n">
         <v>513000</v>
       </c>
+      <c r="Z102" t="n">
+        <v>474612</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0.9251695906432749</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8612,6 +9228,12 @@
       <c r="Y103" t="n">
         <v>512930</v>
       </c>
+      <c r="Z103" t="n">
+        <v>472345</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>0.9208761429434815</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8691,6 +9313,12 @@
       <c r="Y104" t="n">
         <v>1605000</v>
       </c>
+      <c r="Z104" t="n">
+        <v>1232551</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0.7679445482866044</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8770,6 +9398,12 @@
       <c r="Y105" t="n">
         <v>1671000</v>
       </c>
+      <c r="Z105" t="n">
+        <v>1275252</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0.7631669658886894</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8849,6 +9483,12 @@
       <c r="Y106" t="n">
         <v>1725000</v>
       </c>
+      <c r="Z106" t="n">
+        <v>1311029</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0.7600168115942029</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8928,6 +9568,12 @@
       <c r="Y107" t="n">
         <v>1837000</v>
       </c>
+      <c r="Z107" t="n">
+        <v>1405099</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>0.7648878606423517</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9007,6 +9653,12 @@
       <c r="Y108" t="n">
         <v>1986000</v>
       </c>
+      <c r="Z108" t="n">
+        <v>1536854</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>0.7738439073514602</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9086,6 +9738,12 @@
       <c r="Y109" t="n">
         <v>2307300</v>
       </c>
+      <c r="Z109" t="n">
+        <v>1838976</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>0.7970250942660252</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9165,6 +9823,12 @@
       <c r="Y110" t="n">
         <v>3150000</v>
       </c>
+      <c r="Z110" t="n">
+        <v>2153257</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>0.6835736507936508</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9244,6 +9908,12 @@
       <c r="Y111" t="n">
         <v>3286000</v>
       </c>
+      <c r="Z111" t="n">
+        <v>2254337</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>0.6860429093122338</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9323,6 +9993,12 @@
       <c r="Y112" t="n">
         <v>3331000</v>
       </c>
+      <c r="Z112" t="n">
+        <v>2264902</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>0.6799465625938157</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9402,6 +10078,12 @@
       <c r="Y113" t="n">
         <v>3315000</v>
       </c>
+      <c r="Z113" t="n">
+        <v>2222233</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>0.6703568627450981</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9481,6 +10163,12 @@
       <c r="Y114" t="n">
         <v>3464000</v>
       </c>
+      <c r="Z114" t="n">
+        <v>2338446</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>0.6750710161662817</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9560,6 +10248,12 @@
       <c r="Y115" t="n">
         <v>3769154</v>
       </c>
+      <c r="Z115" t="n">
+        <v>2618049</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>0.6945985757016031</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9639,6 +10333,12 @@
       <c r="Y116" t="n">
         <v>447000</v>
       </c>
+      <c r="Z116" t="n">
+        <v>380603</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>0.8514608501118568</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9718,6 +10418,12 @@
       <c r="Y117" t="n">
         <v>468000</v>
       </c>
+      <c r="Z117" t="n">
+        <v>395236</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.8445213675213675</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9797,6 +10503,12 @@
       <c r="Y118" t="n">
         <v>514000</v>
       </c>
+      <c r="Z118" t="n">
+        <v>435146</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.8465875486381323</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9876,6 +10588,12 @@
       <c r="Y119" t="n">
         <v>523000</v>
       </c>
+      <c r="Z119" t="n">
+        <v>439450</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.8402485659655832</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9955,6 +10673,12 @@
       <c r="Y120" t="n">
         <v>553000</v>
       </c>
+      <c r="Z120" t="n">
+        <v>464473</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.8399150090415913</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10034,6 +10758,12 @@
       <c r="Y121" t="n">
         <v>603697</v>
       </c>
+      <c r="Z121" t="n">
+        <v>509458</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.8438968555417701</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10113,6 +10843,12 @@
       <c r="Y122" t="n">
         <v>179000</v>
       </c>
+      <c r="Z122" t="n">
+        <v>160160</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.8947486033519553</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10192,6 +10928,12 @@
       <c r="Y123" t="n">
         <v>192000</v>
       </c>
+      <c r="Z123" t="n">
+        <v>173069</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.9014010416666667</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10271,6 +11013,12 @@
       <c r="Y124" t="n">
         <v>217000</v>
       </c>
+      <c r="Z124" t="n">
+        <v>197564</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.9104331797235024</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10350,6 +11098,12 @@
       <c r="Y125" t="n">
         <v>253000</v>
       </c>
+      <c r="Z125" t="n">
+        <v>233782</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.9240395256916996</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10429,6 +11183,12 @@
       <c r="Y126" t="n">
         <v>246000</v>
       </c>
+      <c r="Z126" t="n">
+        <v>225537</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.9168170731707317</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10508,6 +11268,12 @@
       <c r="Y127" t="n">
         <v>234366</v>
       </c>
+      <c r="Z127" t="n">
+        <v>212712</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.9076060520723995</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10587,6 +11353,12 @@
       <c r="Y128" t="n">
         <v>37000</v>
       </c>
+      <c r="Z128" t="n">
+        <v>33630</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.908918918918919</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10666,6 +11438,12 @@
       <c r="Y129" t="n">
         <v>44000</v>
       </c>
+      <c r="Z129" t="n">
+        <v>40670</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.9243181818181818</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10745,6 +11523,12 @@
       <c r="Y130" t="n">
         <v>47000</v>
       </c>
+      <c r="Z130" t="n">
+        <v>43622</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.9281276595744681</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10824,6 +11608,12 @@
       <c r="Y131" t="n">
         <v>50000</v>
       </c>
+      <c r="Z131" t="n">
+        <v>46522</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.93044</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10903,6 +11693,12 @@
       <c r="Y132" t="n">
         <v>51000</v>
       </c>
+      <c r="Z132" t="n">
+        <v>47386</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.9291372549019608</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10982,6 +11778,12 @@
       <c r="Y133" t="n">
         <v>60471</v>
       </c>
+      <c r="Z133" t="n">
+        <v>56587</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.9357708653734849</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11061,6 +11863,12 @@
       <c r="Y134" t="n">
         <v>1972000</v>
       </c>
+      <c r="Z134" t="n">
+        <v>1568166</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.7952160243407708</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11140,6 +11948,12 @@
       <c r="Y135" t="n">
         <v>2085000</v>
       </c>
+      <c r="Z135" t="n">
+        <v>1673506</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.8026407673860911</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11219,6 +12033,12 @@
       <c r="Y136" t="n">
         <v>2178000</v>
       </c>
+      <c r="Z136" t="n">
+        <v>1758125</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.8072199265381084</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11298,6 +12118,12 @@
       <c r="Y137" t="n">
         <v>2144000</v>
       </c>
+      <c r="Z137" t="n">
+        <v>1713555</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.7992327425373135</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11377,6 +12203,12 @@
       <c r="Y138" t="n">
         <v>2151000</v>
       </c>
+      <c r="Z138" t="n">
+        <v>1709097</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.7945592747559275</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11456,6 +12288,12 @@
       <c r="Y139" t="n">
         <v>2714777</v>
       </c>
+      <c r="Z139" t="n">
+        <v>2263048</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.8336036440562153</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11535,6 +12373,12 @@
       <c r="Y140" t="n">
         <v>1027000</v>
       </c>
+      <c r="Z140" t="n">
+        <v>846398</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.8241460564751704</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11614,6 +12458,12 @@
       <c r="Y141" t="n">
         <v>1173000</v>
       </c>
+      <c r="Z141" t="n">
+        <v>987756</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.842076726342711</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11693,6 +12543,12 @@
       <c r="Y142" t="n">
         <v>1133000</v>
       </c>
+      <c r="Z142" t="n">
+        <v>938409</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.828251544571933</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11772,6 +12628,12 @@
       <c r="Y143" t="n">
         <v>1171000</v>
       </c>
+      <c r="Z143" t="n">
+        <v>969711</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.8281050384286934</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -11851,6 +12713,12 @@
       <c r="Y144" t="n">
         <v>1252000</v>
       </c>
+      <c r="Z144" t="n">
+        <v>1044163</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>0.8339960063897763</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11930,6 +12798,12 @@
       <c r="Y145" t="n">
         <v>1468500</v>
       </c>
+      <c r="Z145" t="n">
+        <v>1253990</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>0.8539257745999319</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -12009,6 +12883,12 @@
       <c r="Y146" t="n">
         <v>243000</v>
       </c>
+      <c r="Z146" t="n">
+        <v>203368</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>0.8369053497942387</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12088,6 +12968,12 @@
       <c r="Y147" t="n">
         <v>233000</v>
       </c>
+      <c r="Z147" t="n">
+        <v>190425</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>0.8172746781115879</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -12167,6 +13053,12 @@
       <c r="Y148" t="n">
         <v>269000</v>
       </c>
+      <c r="Z148" t="n">
+        <v>225137</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>0.8369405204460967</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -12246,6 +13138,12 @@
       <c r="Y149" t="n">
         <v>291000</v>
       </c>
+      <c r="Z149" t="n">
+        <v>245508</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>0.8436701030927835</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -12325,6 +13223,12 @@
       <c r="Y150" t="n">
         <v>284000</v>
       </c>
+      <c r="Z150" t="n">
+        <v>236798</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>0.8337957746478873</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -12404,6 +13308,12 @@
       <c r="Y151" t="n">
         <v>337159</v>
       </c>
+      <c r="Z151" t="n">
+        <v>288429</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>0.85546878475734</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -12483,6 +13393,12 @@
       <c r="Y152" t="n">
         <v>6472000</v>
       </c>
+      <c r="Z152" t="n">
+        <v>4021624</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>0.6213881334981458</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -12562,6 +13478,12 @@
       <c r="Y153" t="n">
         <v>7587000</v>
       </c>
+      <c r="Z153" t="n">
+        <v>5030557</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>0.6630495584552524</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -12641,6 +13563,12 @@
       <c r="Y154" t="n">
         <v>7657000</v>
       </c>
+      <c r="Z154" t="n">
+        <v>5027220</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>0.6565521744808672</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -12720,6 +13648,12 @@
       <c r="Y155" t="n">
         <v>8061000</v>
       </c>
+      <c r="Z155" t="n">
+        <v>5358568</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>0.6647522639870984</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -12799,6 +13733,12 @@
       <c r="Y156" t="n">
         <v>8150000</v>
       </c>
+      <c r="Z156" t="n">
+        <v>5370476</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>0.6589541104294478</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12878,6 +13818,12 @@
       <c r="Y157" t="n">
         <v>9365803</v>
       </c>
+      <c r="Z157" t="n">
+        <v>6502590</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>0.6942907084421912</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -12957,6 +13903,12 @@
       <c r="Y158" t="n">
         <v>180000</v>
       </c>
+      <c r="Z158" t="n">
+        <v>171334</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>0.9518555555555556</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -13036,6 +13988,12 @@
       <c r="Y159" t="n">
         <v>192000</v>
       </c>
+      <c r="Z159" t="n">
+        <v>182465</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>0.9503385416666666</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -13115,6 +14073,12 @@
       <c r="Y160" t="n">
         <v>187000</v>
       </c>
+      <c r="Z160" t="n">
+        <v>177025</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>0.9466577540106952</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -13194,6 +14158,12 @@
       <c r="Y161" t="n">
         <v>186000</v>
       </c>
+      <c r="Z161" t="n">
+        <v>175483</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>0.9434569892473118</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -13273,6 +14243,12 @@
       <c r="Y162" t="n">
         <v>189000</v>
       </c>
+      <c r="Z162" t="n">
+        <v>178220</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>0.942962962962963</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -13351,6 +14327,12 @@
       </c>
       <c r="Y163" t="n">
         <v>220156</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>208683</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>0.9478869528879522</v>
       </c>
     </row>
   </sheetData>
